--- a/Data/cafe.xlsx
+++ b/Data/cafe.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wsand\Documentos\GitHub\Series-de-Tiempo\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF8A5ED4-3708-45A6-BEF2-B5DB097129AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFADFCC0-F473-4A6D-A970-12EBE5354FAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{28C29C7E-C4AB-4C4F-BF87-3F1F1AC8D1B8}"/>
   </bookViews>
@@ -319,9 +319,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="17" fontId="1" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -334,6 +337,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="17" fontId="1" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -731,7 +743,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1627573-E182-4A0B-92BD-CF36B187A2A0}">
-  <dimension ref="A1:B74"/>
+  <dimension ref="A1:B314"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -743,586 +755,2506 @@
       </c>
     </row>
     <row r="2" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A2" s="5">
-        <v>43831</v>
-      </c>
-      <c r="B2" s="6">
-        <v>1050</v>
+      <c r="A2" s="1">
+        <v>36526</v>
+      </c>
+      <c r="B2" s="2">
+        <v>658</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
-        <v>43862</v>
-      </c>
-      <c r="B3" s="7">
-        <v>1001</v>
+        <v>36557</v>
+      </c>
+      <c r="B3" s="3">
+        <v>740</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
-        <v>43891</v>
-      </c>
-      <c r="B4" s="7">
-        <v>806</v>
+        <v>36586</v>
+      </c>
+      <c r="B4" s="3">
+        <v>592</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
-        <v>43922</v>
-      </c>
-      <c r="B5" s="7">
-        <v>744</v>
+        <v>36617</v>
+      </c>
+      <c r="B5" s="3">
+        <v>1055</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
-        <v>43952</v>
-      </c>
-      <c r="B6" s="7">
-        <v>1186</v>
+        <v>36647</v>
+      </c>
+      <c r="B6" s="3">
+        <v>1114</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
-        <v>43983</v>
-      </c>
-      <c r="B7" s="7">
-        <v>1362</v>
+        <v>36678</v>
+      </c>
+      <c r="B7" s="3">
+        <v>1092</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
-        <v>44013</v>
-      </c>
-      <c r="B8" s="7">
-        <v>1310</v>
+        <v>36708</v>
+      </c>
+      <c r="B8" s="3">
+        <v>811</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
-        <v>44044</v>
-      </c>
-      <c r="B9" s="7">
-        <v>1091</v>
+        <v>36739</v>
+      </c>
+      <c r="B9" s="3">
+        <v>436</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
-        <v>44075</v>
-      </c>
-      <c r="B10" s="7">
-        <v>995</v>
+        <v>36770</v>
+      </c>
+      <c r="B10" s="3">
+        <v>501</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
-        <v>44105</v>
-      </c>
-      <c r="B11" s="2">
-        <v>1159</v>
+        <v>36800</v>
+      </c>
+      <c r="B11" s="3">
+        <v>940</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
-        <v>44136</v>
-      </c>
-      <c r="B12" s="2">
-        <v>1443</v>
+        <v>36831</v>
+      </c>
+      <c r="B12" s="3">
+        <v>1366</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="3">
-        <v>44166</v>
-      </c>
-      <c r="B13" s="4">
-        <v>1743</v>
+      <c r="A13" s="4">
+        <v>36861</v>
+      </c>
+      <c r="B13" s="5">
+        <v>1314</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A14" s="5">
-        <v>44197</v>
-      </c>
-      <c r="B14" s="6">
-        <v>1081</v>
+      <c r="A14" s="1">
+        <v>36892</v>
+      </c>
+      <c r="B14" s="2">
+        <v>1231</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
-        <v>44228</v>
-      </c>
-      <c r="B15" s="7">
-        <v>1107</v>
+        <v>36923</v>
+      </c>
+      <c r="B15" s="3">
+        <v>541</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
-        <v>44256</v>
-      </c>
-      <c r="B16" s="7">
-        <v>1050</v>
+        <v>36951</v>
+      </c>
+      <c r="B16" s="3">
+        <v>482</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
-        <v>44287</v>
-      </c>
-      <c r="B17" s="7">
-        <v>810</v>
+        <v>36982</v>
+      </c>
+      <c r="B17" s="3">
+        <v>978</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
-        <v>44317</v>
-      </c>
-      <c r="B18" s="7">
-        <v>616</v>
+        <v>37012</v>
+      </c>
+      <c r="B18" s="3">
+        <v>869</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
-        <v>44348</v>
-      </c>
-      <c r="B19" s="7">
-        <v>1052</v>
+        <v>37043</v>
+      </c>
+      <c r="B19" s="3">
+        <v>718</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
-        <v>44378</v>
-      </c>
-      <c r="B20" s="7">
-        <v>1209</v>
+        <v>37073</v>
+      </c>
+      <c r="B20" s="3">
+        <v>654</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
-        <v>44409</v>
-      </c>
-      <c r="B21" s="7">
-        <v>915</v>
+        <v>37104</v>
+      </c>
+      <c r="B21" s="3">
+        <v>660</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
-        <v>44440</v>
-      </c>
-      <c r="B22" s="7">
-        <v>1209</v>
+        <v>37135</v>
+      </c>
+      <c r="B22" s="3">
+        <v>766</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
-        <v>44470</v>
-      </c>
-      <c r="B23" s="7">
-        <v>1012</v>
+        <v>37165</v>
+      </c>
+      <c r="B23" s="3">
+        <v>1243</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
-        <v>44501</v>
-      </c>
-      <c r="B24" s="7">
-        <v>1131</v>
+        <v>37196</v>
+      </c>
+      <c r="B24" s="3">
+        <v>1537</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="3">
-        <v>44531</v>
-      </c>
-      <c r="B25" s="8">
-        <v>1385</v>
+      <c r="A25" s="4">
+        <v>37226</v>
+      </c>
+      <c r="B25" s="5">
+        <v>1257</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
-        <v>44562</v>
-      </c>
-      <c r="B26" s="7">
-        <v>868</v>
+        <v>37257</v>
+      </c>
+      <c r="B26" s="2">
+        <v>824</v>
       </c>
     </row>
     <row r="27" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
-        <v>44593</v>
-      </c>
-      <c r="B27" s="7">
-        <v>928</v>
+        <v>37288</v>
+      </c>
+      <c r="B27" s="3">
+        <v>808</v>
       </c>
     </row>
     <row r="28" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
-        <v>44621</v>
-      </c>
-      <c r="B28" s="7">
-        <v>914</v>
+        <v>37316</v>
+      </c>
+      <c r="B28" s="3">
+        <v>778</v>
       </c>
     </row>
     <row r="29" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
-        <v>44652</v>
-      </c>
-      <c r="B29" s="7">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" ht="16.8" x14ac:dyDescent="0.4">
+        <v>37347</v>
+      </c>
+      <c r="B29" s="3">
+        <v>942</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
-        <v>44682</v>
-      </c>
-      <c r="B30" s="9">
-        <v>1017</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" ht="16.8" x14ac:dyDescent="0.4">
+        <v>37377</v>
+      </c>
+      <c r="B30" s="3">
+        <v>1112</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
-        <v>44713</v>
-      </c>
-      <c r="B31" s="9">
-        <v>951</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" ht="16.8" x14ac:dyDescent="0.4">
+        <v>37408</v>
+      </c>
+      <c r="B31" s="3">
+        <v>1052</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
-        <v>44743</v>
-      </c>
-      <c r="B32" s="9">
-        <v>943.59922018886186</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" ht="16.8" x14ac:dyDescent="0.4">
+        <v>37438</v>
+      </c>
+      <c r="B32" s="3">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
-        <v>44774</v>
-      </c>
-      <c r="B33" s="9">
-        <v>949</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" ht="16.8" x14ac:dyDescent="0.4">
+        <v>37469</v>
+      </c>
+      <c r="B33" s="3">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
-        <v>44805</v>
-      </c>
-      <c r="B34" s="9">
-        <v>834</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" ht="16.8" x14ac:dyDescent="0.4">
+        <v>37500</v>
+      </c>
+      <c r="B34" s="3">
+        <v>778</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
-        <v>44835</v>
-      </c>
-      <c r="B35" s="9">
-        <v>888</v>
+        <v>37530</v>
+      </c>
+      <c r="B35" s="3">
+        <v>1064</v>
       </c>
     </row>
     <row r="36" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
+        <v>37561</v>
+      </c>
+      <c r="B36" s="3">
+        <v>1380</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="4">
+        <v>37591</v>
+      </c>
+      <c r="B37" s="5">
+        <v>1257</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A38" s="1">
+        <v>37622</v>
+      </c>
+      <c r="B38" s="2">
+        <v>924</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A39" s="1">
+        <v>37653</v>
+      </c>
+      <c r="B39" s="3">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A40" s="1">
+        <v>37681</v>
+      </c>
+      <c r="B40" s="3">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A41" s="1">
+        <v>37712</v>
+      </c>
+      <c r="B41" s="3">
+        <v>1078</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A42" s="1">
+        <v>37742</v>
+      </c>
+      <c r="B42" s="3">
+        <v>972</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A43" s="1">
+        <v>37773</v>
+      </c>
+      <c r="B43" s="3">
+        <v>1077</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A44" s="1">
+        <v>37803</v>
+      </c>
+      <c r="B44" s="3">
+        <v>1072</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A45" s="1">
+        <v>37834</v>
+      </c>
+      <c r="B45" s="3">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A46" s="1">
+        <v>37865</v>
+      </c>
+      <c r="B46" s="3">
+        <v>795</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A47" s="1">
+        <v>37895</v>
+      </c>
+      <c r="B47" s="3">
+        <v>1137</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A48" s="1">
+        <v>37926</v>
+      </c>
+      <c r="B48" s="3">
+        <v>1176</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A49" s="4">
+        <v>37956</v>
+      </c>
+      <c r="B49" s="5">
+        <v>1244</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A50" s="1">
+        <v>37987</v>
+      </c>
+      <c r="B50" s="2">
+        <v>1171</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A51" s="1">
+        <v>38018</v>
+      </c>
+      <c r="B51" s="3">
+        <v>770</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A52" s="1">
+        <v>38047</v>
+      </c>
+      <c r="B52" s="3">
+        <v>811</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A53" s="1">
+        <v>38078</v>
+      </c>
+      <c r="B53" s="3">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A54" s="1">
+        <v>38108</v>
+      </c>
+      <c r="B54" s="3">
+        <v>1091</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A55" s="1">
+        <v>38139</v>
+      </c>
+      <c r="B55" s="3">
+        <v>954</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A56" s="1">
+        <v>38169</v>
+      </c>
+      <c r="B56" s="3">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A57" s="1">
+        <v>38200</v>
+      </c>
+      <c r="B57" s="3">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A58" s="1">
+        <v>38231</v>
+      </c>
+      <c r="B58" s="3">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A59" s="1">
+        <v>38261</v>
+      </c>
+      <c r="B59" s="3">
+        <v>1077</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A60" s="1">
+        <v>38292</v>
+      </c>
+      <c r="B60" s="3">
+        <v>1337</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A61" s="4">
+        <v>38322</v>
+      </c>
+      <c r="B61" s="5">
+        <v>1330</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A62" s="1">
+        <v>38353</v>
+      </c>
+      <c r="B62" s="2">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A63" s="1">
+        <v>38384</v>
+      </c>
+      <c r="B63" s="3">
+        <v>1023</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A64" s="1">
+        <v>38412</v>
+      </c>
+      <c r="B64" s="3">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A65" s="1">
+        <v>38443</v>
+      </c>
+      <c r="B65" s="3">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A66" s="1">
+        <v>38473</v>
+      </c>
+      <c r="B66" s="3">
+        <v>955</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A67" s="1">
+        <v>38504</v>
+      </c>
+      <c r="B67" s="3">
+        <v>948</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A68" s="1">
+        <v>38534</v>
+      </c>
+      <c r="B68" s="3">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A69" s="1">
+        <v>38565</v>
+      </c>
+      <c r="B69" s="3">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A70" s="1">
+        <v>38596</v>
+      </c>
+      <c r="B70" s="3">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A71" s="1">
+        <v>38626</v>
+      </c>
+      <c r="B71" s="3">
+        <v>1131</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A72" s="1">
+        <v>38657</v>
+      </c>
+      <c r="B72" s="3">
+        <v>1237</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A73" s="4">
+        <v>38687</v>
+      </c>
+      <c r="B73" s="5">
+        <v>1066</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A74" s="1">
+        <v>38718</v>
+      </c>
+      <c r="B74" s="2">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A75" s="1">
+        <v>38749</v>
+      </c>
+      <c r="B75" s="3">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A76" s="1">
+        <v>38777</v>
+      </c>
+      <c r="B76" s="3">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A77" s="1">
+        <v>38808</v>
+      </c>
+      <c r="B77" s="3">
+        <v>778.5</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A78" s="1">
+        <v>38838</v>
+      </c>
+      <c r="B78" s="3">
+        <v>1087</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A79" s="1">
+        <v>38869</v>
+      </c>
+      <c r="B79" s="3">
+        <v>1174</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A80" s="1">
+        <v>38899</v>
+      </c>
+      <c r="B80" s="3">
+        <v>820.5</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A81" s="1">
+        <v>38930</v>
+      </c>
+      <c r="B81" s="3">
+        <v>1142</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A82" s="1">
+        <v>38961</v>
+      </c>
+      <c r="B82" s="3">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A83" s="1">
+        <v>38991</v>
+      </c>
+      <c r="B83" s="3">
+        <v>1024</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A84" s="1">
+        <v>39022</v>
+      </c>
+      <c r="B84" s="3">
+        <v>1242</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A85" s="4">
+        <v>39052</v>
+      </c>
+      <c r="B85" s="5">
+        <v>1294</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A86" s="1">
+        <v>39083</v>
+      </c>
+      <c r="B86" s="2">
+        <v>963</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A87" s="1">
+        <v>39114</v>
+      </c>
+      <c r="B87" s="3">
+        <v>1001</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A88" s="1">
+        <v>39142</v>
+      </c>
+      <c r="B88" s="3">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A89" s="1">
+        <v>39173</v>
+      </c>
+      <c r="B89" s="3">
+        <v>769</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A90" s="1">
+        <v>39203</v>
+      </c>
+      <c r="B90" s="3">
+        <v>994</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A91" s="1">
+        <v>39234</v>
+      </c>
+      <c r="B91" s="3">
+        <v>1219</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A92" s="1">
+        <v>39264</v>
+      </c>
+      <c r="B92" s="3">
+        <v>995</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A93" s="1">
+        <v>39295</v>
+      </c>
+      <c r="B93" s="3">
+        <v>990</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A94" s="1">
+        <v>39326</v>
+      </c>
+      <c r="B94" s="3">
+        <v>897</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A95" s="1">
+        <v>39356</v>
+      </c>
+      <c r="B95" s="3">
+        <v>1129</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A96" s="1">
+        <v>39387</v>
+      </c>
+      <c r="B96" s="3">
+        <v>1522</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A97" s="4">
+        <v>39417</v>
+      </c>
+      <c r="B97" s="5">
+        <v>1363</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A98" s="1">
+        <v>39448</v>
+      </c>
+      <c r="B98" s="2">
+        <v>1404</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A99" s="1">
+        <v>39479</v>
+      </c>
+      <c r="B99" s="3">
+        <v>1090</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A100" s="1">
+        <v>39508</v>
+      </c>
+      <c r="B100" s="3">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A101" s="1">
+        <v>39539</v>
+      </c>
+      <c r="B101" s="3">
+        <v>886</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A102" s="1">
+        <v>39569</v>
+      </c>
+      <c r="B102" s="3">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A103" s="1">
+        <v>39600</v>
+      </c>
+      <c r="B103" s="3">
+        <v>1046</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A104" s="1">
+        <v>39630</v>
+      </c>
+      <c r="B104" s="3">
+        <v>891</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A105" s="1">
+        <v>39661</v>
+      </c>
+      <c r="B105" s="3">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A106" s="1">
+        <v>39692</v>
+      </c>
+      <c r="B106" s="3">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A107" s="1">
+        <v>39722</v>
+      </c>
+      <c r="B107" s="3">
+        <v>939</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A108" s="1">
+        <v>39753</v>
+      </c>
+      <c r="B108" s="3">
+        <v>933</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A109" s="1">
+        <v>39783</v>
+      </c>
+      <c r="B109" s="5">
+        <v>1105</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A110" s="6">
+        <v>39814</v>
+      </c>
+      <c r="B110" s="2">
+        <v>876</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A111" s="1">
+        <v>39845</v>
+      </c>
+      <c r="B111" s="3">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A112" s="1">
+        <v>39873</v>
+      </c>
+      <c r="B112" s="3">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A113" s="1">
+        <v>39904</v>
+      </c>
+      <c r="B113" s="3">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A114" s="1">
+        <v>39934</v>
+      </c>
+      <c r="B114" s="3">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A115" s="1">
+        <v>39965</v>
+      </c>
+      <c r="B115" s="3">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A116" s="1">
+        <v>39995</v>
+      </c>
+      <c r="B116" s="3">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A117" s="1">
+        <v>40026</v>
+      </c>
+      <c r="B117" s="3">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A118" s="1">
+        <v>40057</v>
+      </c>
+      <c r="B118" s="3">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A119" s="1">
+        <v>40087</v>
+      </c>
+      <c r="B119" s="3">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A120" s="1">
+        <v>40118</v>
+      </c>
+      <c r="B120" s="3">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A121" s="4">
+        <v>40148</v>
+      </c>
+      <c r="B121" s="5">
+        <v>821</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A122" s="1">
+        <v>40179</v>
+      </c>
+      <c r="B122" s="7">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A123" s="1">
+        <v>40210</v>
+      </c>
+      <c r="B123" s="8">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A124" s="1">
+        <v>40238</v>
+      </c>
+      <c r="B124" s="8">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A125" s="1">
+        <v>40269</v>
+      </c>
+      <c r="B125" s="8">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A126" s="1">
+        <v>40299</v>
+      </c>
+      <c r="B126" s="8">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A127" s="1">
+        <v>40330</v>
+      </c>
+      <c r="B127" s="8">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A128" s="1">
+        <v>40360</v>
+      </c>
+      <c r="B128" s="8">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A129" s="1">
+        <v>40391</v>
+      </c>
+      <c r="B129" s="8">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A130" s="1">
+        <v>40422</v>
+      </c>
+      <c r="B130" s="8">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A131" s="1">
+        <v>40452</v>
+      </c>
+      <c r="B131" s="8">
+        <v>807</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A132" s="1">
+        <v>40483</v>
+      </c>
+      <c r="B132" s="8">
+        <v>979</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A133" s="4">
+        <v>40513</v>
+      </c>
+      <c r="B133" s="5">
+        <v>1164</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A134" s="1">
+        <v>40544</v>
+      </c>
+      <c r="B134" s="7">
+        <v>908</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A135" s="1">
+        <v>40575</v>
+      </c>
+      <c r="B135" s="8">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A136" s="1">
+        <v>40603</v>
+      </c>
+      <c r="B136" s="8">
+        <v>779</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A137" s="1">
+        <v>40634</v>
+      </c>
+      <c r="B137" s="8">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A138" s="1">
+        <v>40664</v>
+      </c>
+      <c r="B138" s="8">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A139" s="1">
+        <v>40695</v>
+      </c>
+      <c r="B139" s="8">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A140" s="1">
+        <v>40725</v>
+      </c>
+      <c r="B140" s="8">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A141" s="1">
+        <v>40756</v>
+      </c>
+      <c r="B141" s="8">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A142" s="1">
+        <v>40787</v>
+      </c>
+      <c r="B142" s="8">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A143" s="1">
+        <v>40817</v>
+      </c>
+      <c r="B143" s="8">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A144" s="1">
+        <v>40848</v>
+      </c>
+      <c r="B144" s="8">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A145" s="4">
+        <v>40878</v>
+      </c>
+      <c r="B145" s="5">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A146" s="1">
+        <v>40909</v>
+      </c>
+      <c r="B146" s="7">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A147" s="1">
+        <v>40940</v>
+      </c>
+      <c r="B147" s="8">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A148" s="1">
+        <v>40969</v>
+      </c>
+      <c r="B148" s="8">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A149" s="1">
+        <v>41000</v>
+      </c>
+      <c r="B149" s="8">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A150" s="1">
+        <v>41030</v>
+      </c>
+      <c r="B150" s="8">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A151" s="1">
+        <v>41061</v>
+      </c>
+      <c r="B151" s="8">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A152" s="1">
+        <v>41091</v>
+      </c>
+      <c r="B152" s="8">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A153" s="1">
+        <v>41122</v>
+      </c>
+      <c r="B153" s="8">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A154" s="1">
+        <v>41153</v>
+      </c>
+      <c r="B154" s="8">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A155" s="1">
+        <v>41183</v>
+      </c>
+      <c r="B155" s="8">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A156" s="1">
+        <v>41214</v>
+      </c>
+      <c r="B156" s="8">
+        <v>770</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A157" s="4">
+        <v>41244</v>
+      </c>
+      <c r="B157" s="9">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A158" s="1">
+        <v>41275</v>
+      </c>
+      <c r="B158" s="7">
+        <v>877</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A159" s="1">
+        <v>41306</v>
+      </c>
+      <c r="B159" s="8">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A160" s="1">
+        <v>41334</v>
+      </c>
+      <c r="B160" s="8">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A161" s="1">
+        <v>41365</v>
+      </c>
+      <c r="B161" s="8">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A162" s="1">
+        <v>41395</v>
+      </c>
+      <c r="B162" s="8">
+        <v>937</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A163" s="1">
+        <v>41426</v>
+      </c>
+      <c r="B163" s="8">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A164" s="1">
+        <v>41456</v>
+      </c>
+      <c r="B164" s="3">
+        <v>1031</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A165" s="1">
+        <v>41487</v>
+      </c>
+      <c r="B165" s="3">
+        <v>770</v>
+      </c>
+    </row>
+    <row r="166" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A166" s="1">
+        <v>41518</v>
+      </c>
+      <c r="B166" s="3">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="167" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A167" s="1">
+        <v>41548</v>
+      </c>
+      <c r="B167" s="3">
+        <v>1058</v>
+      </c>
+    </row>
+    <row r="168" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A168" s="1">
+        <v>41579</v>
+      </c>
+      <c r="B168" s="3">
+        <v>1113</v>
+      </c>
+    </row>
+    <row r="169" spans="1:2" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A169" s="4">
+        <v>41609</v>
+      </c>
+      <c r="B169" s="5">
+        <v>1115</v>
+      </c>
+    </row>
+    <row r="170" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A170" s="1">
+        <v>41640</v>
+      </c>
+      <c r="B170" s="7">
+        <v>1011</v>
+      </c>
+    </row>
+    <row r="171" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A171" s="1">
+        <v>41671</v>
+      </c>
+      <c r="B171" s="3">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="172" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A172" s="1">
+        <v>41699</v>
+      </c>
+      <c r="B172" s="3">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="173" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A173" s="1">
+        <v>41730</v>
+      </c>
+      <c r="B173" s="3">
+        <v>832</v>
+      </c>
+    </row>
+    <row r="174" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A174" s="1">
+        <v>41760</v>
+      </c>
+      <c r="B174" s="3">
+        <v>1050</v>
+      </c>
+    </row>
+    <row r="175" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A175" s="1">
+        <v>41791</v>
+      </c>
+      <c r="B175" s="3">
+        <v>944</v>
+      </c>
+    </row>
+    <row r="176" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A176" s="1">
+        <v>41821</v>
+      </c>
+      <c r="B176" s="3">
+        <v>1236</v>
+      </c>
+    </row>
+    <row r="177" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A177" s="1">
+        <v>41852</v>
+      </c>
+      <c r="B177" s="3">
+        <v>1151</v>
+      </c>
+    </row>
+    <row r="178" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A178" s="1">
+        <v>41883</v>
+      </c>
+      <c r="B178" s="3">
+        <v>912</v>
+      </c>
+    </row>
+    <row r="179" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A179" s="1">
+        <v>41913</v>
+      </c>
+      <c r="B179" s="3">
+        <v>1101</v>
+      </c>
+    </row>
+    <row r="180" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A180" s="1">
+        <v>41944</v>
+      </c>
+      <c r="B180" s="3">
+        <v>1115</v>
+      </c>
+    </row>
+    <row r="181" spans="1:2" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A181" s="4">
+        <v>41974</v>
+      </c>
+      <c r="B181" s="5">
+        <v>1086</v>
+      </c>
+    </row>
+    <row r="182" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A182" s="1">
+        <v>42005</v>
+      </c>
+      <c r="B182" s="7">
+        <v>1088</v>
+      </c>
+    </row>
+    <row r="183" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A183" s="1">
+        <v>42036</v>
+      </c>
+      <c r="B183" s="3">
+        <v>1029</v>
+      </c>
+    </row>
+    <row r="184" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A184" s="1">
+        <v>42064</v>
+      </c>
+      <c r="B184" s="3">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="185" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A185" s="1">
+        <v>42095</v>
+      </c>
+      <c r="B185" s="3">
+        <v>924</v>
+      </c>
+    </row>
+    <row r="186" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A186" s="1">
+        <v>42125</v>
+      </c>
+      <c r="B186" s="3">
+        <v>1165</v>
+      </c>
+    </row>
+    <row r="187" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A187" s="1">
+        <v>42156</v>
+      </c>
+      <c r="B187" s="3">
+        <v>1240</v>
+      </c>
+    </row>
+    <row r="188" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A188" s="1">
+        <v>42186</v>
+      </c>
+      <c r="B188" s="3">
+        <v>1463</v>
+      </c>
+    </row>
+    <row r="189" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A189" s="1">
+        <v>42217</v>
+      </c>
+      <c r="B189" s="3">
+        <v>1264</v>
+      </c>
+    </row>
+    <row r="190" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A190" s="1">
+        <v>42248</v>
+      </c>
+      <c r="B190" s="3">
+        <v>1058</v>
+      </c>
+    </row>
+    <row r="191" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A191" s="1">
+        <v>42278</v>
+      </c>
+      <c r="B191" s="3">
+        <v>1368</v>
+      </c>
+    </row>
+    <row r="192" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A192" s="1">
+        <v>42309</v>
+      </c>
+      <c r="B192" s="3">
+        <v>1322</v>
+      </c>
+    </row>
+    <row r="193" spans="1:2" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A193" s="4">
+        <v>42339</v>
+      </c>
+      <c r="B193" s="5">
+        <v>1454</v>
+      </c>
+    </row>
+    <row r="194" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A194" s="1">
+        <v>42370</v>
+      </c>
+      <c r="B194" s="3">
+        <v>1136</v>
+      </c>
+    </row>
+    <row r="195" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A195" s="1">
+        <v>42401</v>
+      </c>
+      <c r="B195" s="3">
+        <v>1096</v>
+      </c>
+    </row>
+    <row r="196" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A196" s="1">
+        <v>42430</v>
+      </c>
+      <c r="B196" s="3">
+        <v>944</v>
+      </c>
+    </row>
+    <row r="197" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A197" s="1">
+        <v>42461</v>
+      </c>
+      <c r="B197" s="3">
+        <v>1043</v>
+      </c>
+    </row>
+    <row r="198" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A198" s="1">
+        <v>42491</v>
+      </c>
+      <c r="B198" s="3">
+        <v>1163</v>
+      </c>
+    </row>
+    <row r="199" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A199" s="1">
+        <v>42522</v>
+      </c>
+      <c r="B199" s="3">
+        <v>1158</v>
+      </c>
+    </row>
+    <row r="200" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A200" s="1">
+        <v>42552</v>
+      </c>
+      <c r="B200" s="3">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="201" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A201" s="1">
+        <v>42583</v>
+      </c>
+      <c r="B201" s="3">
+        <v>1189</v>
+      </c>
+    </row>
+    <row r="202" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A202" s="1">
+        <v>42614</v>
+      </c>
+      <c r="B202" s="3">
+        <v>1034</v>
+      </c>
+    </row>
+    <row r="203" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A203" s="1">
+        <v>42644</v>
+      </c>
+      <c r="B203" s="3">
+        <v>1395</v>
+      </c>
+    </row>
+    <row r="204" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A204" s="1">
+        <v>42675</v>
+      </c>
+      <c r="B204" s="3">
+        <v>1653</v>
+      </c>
+    </row>
+    <row r="205" spans="1:2" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A205" s="4">
+        <v>42705</v>
+      </c>
+      <c r="B205" s="5">
+        <v>1319</v>
+      </c>
+    </row>
+    <row r="206" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A206" s="6">
+        <v>42736</v>
+      </c>
+      <c r="B206" s="2">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="207" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A207" s="1">
+        <v>42767</v>
+      </c>
+      <c r="B207" s="3">
+        <v>1293</v>
+      </c>
+    </row>
+    <row r="208" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A208" s="1">
+        <v>42795</v>
+      </c>
+      <c r="B208" s="3">
+        <v>1020</v>
+      </c>
+    </row>
+    <row r="209" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A209" s="1">
+        <v>42826</v>
+      </c>
+      <c r="B209" s="3">
+        <v>834</v>
+      </c>
+    </row>
+    <row r="210" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A210" s="1">
+        <v>42856</v>
+      </c>
+      <c r="B210" s="3">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="211" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A211" s="1">
+        <v>42887</v>
+      </c>
+      <c r="B211" s="3">
+        <v>1049</v>
+      </c>
+    </row>
+    <row r="212" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A212" s="1">
+        <v>42917</v>
+      </c>
+      <c r="B212" s="3">
+        <v>1373</v>
+      </c>
+    </row>
+    <row r="213" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A213" s="1">
+        <v>42948</v>
+      </c>
+      <c r="B213" s="3">
+        <v>1294</v>
+      </c>
+    </row>
+    <row r="214" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A214" s="1">
+        <v>42979</v>
+      </c>
+      <c r="B214" s="3">
+        <v>1228</v>
+      </c>
+    </row>
+    <row r="215" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A215" s="1">
+        <v>43009</v>
+      </c>
+      <c r="B215" s="3">
+        <v>1073</v>
+      </c>
+    </row>
+    <row r="216" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A216" s="1">
+        <v>43040</v>
+      </c>
+      <c r="B216" s="3">
+        <v>1304</v>
+      </c>
+    </row>
+    <row r="217" spans="1:2" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A217" s="4">
+        <v>43070</v>
+      </c>
+      <c r="B217" s="5">
+        <v>1550</v>
+      </c>
+    </row>
+    <row r="218" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A218" s="6">
+        <v>43101</v>
+      </c>
+      <c r="B218" s="2">
+        <v>1131</v>
+      </c>
+    </row>
+    <row r="219" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A219" s="1">
+        <v>43132</v>
+      </c>
+      <c r="B219" s="3">
+        <v>1212</v>
+      </c>
+    </row>
+    <row r="220" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A220" s="1">
+        <v>43160</v>
+      </c>
+      <c r="B220" s="3">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="221" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A221" s="1">
+        <v>43191</v>
+      </c>
+      <c r="B221" s="3">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="222" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A222" s="1">
+        <v>43221</v>
+      </c>
+      <c r="B222" s="3">
+        <v>1188</v>
+      </c>
+    </row>
+    <row r="223" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A223" s="1">
+        <v>43252</v>
+      </c>
+      <c r="B223" s="3">
+        <v>1087</v>
+      </c>
+    </row>
+    <row r="224" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A224" s="1">
+        <v>43282</v>
+      </c>
+      <c r="B224" s="3">
+        <v>1051</v>
+      </c>
+    </row>
+    <row r="225" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A225" s="1">
+        <v>43313</v>
+      </c>
+      <c r="B225" s="3">
+        <v>1258</v>
+      </c>
+    </row>
+    <row r="226" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A226" s="1">
+        <v>43344</v>
+      </c>
+      <c r="B226" s="3">
+        <v>1050</v>
+      </c>
+    </row>
+    <row r="227" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A227" s="1">
+        <v>43374</v>
+      </c>
+      <c r="B227" s="3">
+        <v>1086</v>
+      </c>
+    </row>
+    <row r="228" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A228" s="1">
+        <v>43405</v>
+      </c>
+      <c r="B228" s="3">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="229" spans="1:2" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A229" s="4">
+        <v>43435</v>
+      </c>
+      <c r="B229" s="5">
+        <v>1283</v>
+      </c>
+    </row>
+    <row r="230" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A230" s="6">
+        <v>43466</v>
+      </c>
+      <c r="B230" s="10">
+        <v>1296</v>
+      </c>
+    </row>
+    <row r="231" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A231" s="1">
+        <v>43497</v>
+      </c>
+      <c r="B231" s="11">
+        <v>1106</v>
+      </c>
+    </row>
+    <row r="232" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A232" s="1">
+        <v>43525</v>
+      </c>
+      <c r="B232" s="11">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="233" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A233" s="1">
+        <v>43556</v>
+      </c>
+      <c r="B233" s="11">
+        <v>1031</v>
+      </c>
+    </row>
+    <row r="234" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A234" s="1">
+        <v>43586</v>
+      </c>
+      <c r="B234" s="11">
+        <v>1115</v>
+      </c>
+    </row>
+    <row r="235" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A235" s="1">
+        <v>43617</v>
+      </c>
+      <c r="B235" s="11">
+        <v>1211</v>
+      </c>
+    </row>
+    <row r="236" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A236" s="1">
+        <v>43647</v>
+      </c>
+      <c r="B236" s="11">
+        <v>1317</v>
+      </c>
+    </row>
+    <row r="237" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A237" s="1">
+        <v>43678</v>
+      </c>
+      <c r="B237" s="11">
+        <v>1119</v>
+      </c>
+    </row>
+    <row r="238" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A238" s="1">
+        <v>43709</v>
+      </c>
+      <c r="B238" s="11">
+        <v>1088</v>
+      </c>
+    </row>
+    <row r="239" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A239" s="1">
+        <v>43739</v>
+      </c>
+      <c r="B239" s="3">
+        <v>1369</v>
+      </c>
+    </row>
+    <row r="240" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A240" s="1">
+        <v>43770</v>
+      </c>
+      <c r="B240" s="3">
+        <v>1506</v>
+      </c>
+    </row>
+    <row r="241" spans="1:2" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A241" s="4">
+        <v>43800</v>
+      </c>
+      <c r="B241" s="5">
+        <v>1680</v>
+      </c>
+    </row>
+    <row r="242" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A242" s="6">
+        <v>43831</v>
+      </c>
+      <c r="B242" s="10">
+        <v>1050</v>
+      </c>
+    </row>
+    <row r="243" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A243" s="1">
+        <v>43862</v>
+      </c>
+      <c r="B243" s="11">
+        <v>1001</v>
+      </c>
+    </row>
+    <row r="244" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A244" s="1">
+        <v>43891</v>
+      </c>
+      <c r="B244" s="11">
+        <v>806</v>
+      </c>
+    </row>
+    <row r="245" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A245" s="1">
+        <v>43922</v>
+      </c>
+      <c r="B245" s="11">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="246" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A246" s="1">
+        <v>43952</v>
+      </c>
+      <c r="B246" s="11">
+        <v>1186</v>
+      </c>
+    </row>
+    <row r="247" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A247" s="1">
+        <v>43983</v>
+      </c>
+      <c r="B247" s="11">
+        <v>1362</v>
+      </c>
+    </row>
+    <row r="248" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A248" s="1">
+        <v>44013</v>
+      </c>
+      <c r="B248" s="11">
+        <v>1310</v>
+      </c>
+    </row>
+    <row r="249" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A249" s="1">
+        <v>44044</v>
+      </c>
+      <c r="B249" s="11">
+        <v>1091</v>
+      </c>
+    </row>
+    <row r="250" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A250" s="1">
+        <v>44075</v>
+      </c>
+      <c r="B250" s="11">
+        <v>995</v>
+      </c>
+    </row>
+    <row r="251" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A251" s="1">
+        <v>44105</v>
+      </c>
+      <c r="B251" s="3">
+        <v>1159</v>
+      </c>
+    </row>
+    <row r="252" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A252" s="1">
+        <v>44136</v>
+      </c>
+      <c r="B252" s="3">
+        <v>1443</v>
+      </c>
+    </row>
+    <row r="253" spans="1:2" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A253" s="4">
+        <v>44166</v>
+      </c>
+      <c r="B253" s="5">
+        <v>1743</v>
+      </c>
+    </row>
+    <row r="254" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A254" s="6">
+        <v>44197</v>
+      </c>
+      <c r="B254" s="10">
+        <v>1081</v>
+      </c>
+    </row>
+    <row r="255" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A255" s="1">
+        <v>44228</v>
+      </c>
+      <c r="B255" s="11">
+        <v>1107</v>
+      </c>
+    </row>
+    <row r="256" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A256" s="1">
+        <v>44256</v>
+      </c>
+      <c r="B256" s="11">
+        <v>1050</v>
+      </c>
+    </row>
+    <row r="257" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A257" s="1">
+        <v>44287</v>
+      </c>
+      <c r="B257" s="11">
+        <v>810</v>
+      </c>
+    </row>
+    <row r="258" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A258" s="1">
+        <v>44317</v>
+      </c>
+      <c r="B258" s="11">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="259" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A259" s="1">
+        <v>44348</v>
+      </c>
+      <c r="B259" s="11">
+        <v>1052</v>
+      </c>
+    </row>
+    <row r="260" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A260" s="1">
+        <v>44378</v>
+      </c>
+      <c r="B260" s="11">
+        <v>1209</v>
+      </c>
+    </row>
+    <row r="261" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A261" s="1">
+        <v>44409</v>
+      </c>
+      <c r="B261" s="11">
+        <v>915</v>
+      </c>
+    </row>
+    <row r="262" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A262" s="1">
+        <v>44440</v>
+      </c>
+      <c r="B262" s="11">
+        <v>1209</v>
+      </c>
+    </row>
+    <row r="263" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A263" s="1">
+        <v>44470</v>
+      </c>
+      <c r="B263" s="11">
+        <v>1012</v>
+      </c>
+    </row>
+    <row r="264" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A264" s="1">
+        <v>44501</v>
+      </c>
+      <c r="B264" s="11">
+        <v>1131</v>
+      </c>
+    </row>
+    <row r="265" spans="1:2" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A265" s="4">
+        <v>44531</v>
+      </c>
+      <c r="B265" s="12">
+        <v>1385</v>
+      </c>
+    </row>
+    <row r="266" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A266" s="1">
+        <v>44562</v>
+      </c>
+      <c r="B266" s="11">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="267" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A267" s="1">
+        <v>44593</v>
+      </c>
+      <c r="B267" s="11">
+        <v>928</v>
+      </c>
+    </row>
+    <row r="268" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A268" s="1">
+        <v>44621</v>
+      </c>
+      <c r="B268" s="11">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="269" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A269" s="1">
+        <v>44652</v>
+      </c>
+      <c r="B269" s="11">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="270" spans="1:2" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A270" s="1">
+        <v>44682</v>
+      </c>
+      <c r="B270" s="13">
+        <v>1017</v>
+      </c>
+    </row>
+    <row r="271" spans="1:2" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A271" s="1">
+        <v>44713</v>
+      </c>
+      <c r="B271" s="13">
+        <v>951</v>
+      </c>
+    </row>
+    <row r="272" spans="1:2" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A272" s="1">
+        <v>44743</v>
+      </c>
+      <c r="B272" s="13">
+        <v>943.59922018886186</v>
+      </c>
+    </row>
+    <row r="273" spans="1:2" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A273" s="1">
+        <v>44774</v>
+      </c>
+      <c r="B273" s="13">
+        <v>949</v>
+      </c>
+    </row>
+    <row r="274" spans="1:2" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A274" s="1">
+        <v>44805</v>
+      </c>
+      <c r="B274" s="13">
+        <v>834</v>
+      </c>
+    </row>
+    <row r="275" spans="1:2" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A275" s="1">
+        <v>44835</v>
+      </c>
+      <c r="B275" s="13">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="276" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A276" s="1">
         <v>44866</v>
       </c>
-      <c r="B36" s="7">
+      <c r="B276" s="11">
         <v>1060</v>
       </c>
     </row>
-    <row r="37" spans="1:2" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="1">
+    <row r="277" spans="1:2" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A277" s="1">
         <v>44896</v>
       </c>
-      <c r="B37" s="7">
+      <c r="B277" s="11">
         <v>981</v>
       </c>
     </row>
-    <row r="38" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A38" s="11">
+    <row r="278" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A278" s="15">
         <v>44927</v>
       </c>
-      <c r="B38" s="12">
+      <c r="B278" s="16">
         <v>868</v>
       </c>
     </row>
-    <row r="39" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A39" s="13">
+    <row r="279" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A279" s="17">
         <v>44958</v>
       </c>
-      <c r="B39" s="14">
+      <c r="B279" s="18">
         <v>1025</v>
       </c>
     </row>
-    <row r="40" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A40" s="13">
+    <row r="280" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A280" s="17">
         <v>44986</v>
       </c>
-      <c r="B40" s="14">
+      <c r="B280" s="18">
         <v>799</v>
       </c>
     </row>
-    <row r="41" spans="1:2" ht="16.8" x14ac:dyDescent="0.4">
-      <c r="A41" s="13">
+    <row r="281" spans="1:2" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A281" s="17">
         <v>45017</v>
       </c>
-      <c r="B41" s="15">
+      <c r="B281" s="19">
         <v>565.867207197894</v>
       </c>
     </row>
-    <row r="42" spans="1:2" ht="16.8" x14ac:dyDescent="0.4">
-      <c r="A42" s="13">
+    <row r="282" spans="1:2" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A282" s="17">
         <v>45047</v>
       </c>
-      <c r="B42" s="15">
+      <c r="B282" s="19">
         <v>806.19550573311096</v>
       </c>
     </row>
-    <row r="43" spans="1:2" ht="16.8" x14ac:dyDescent="0.4">
-      <c r="A43" s="13">
+    <row r="283" spans="1:2" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A283" s="17">
         <v>45078</v>
       </c>
-      <c r="B43" s="15">
+      <c r="B283" s="19">
         <v>956</v>
       </c>
     </row>
-    <row r="44" spans="1:2" ht="16.8" x14ac:dyDescent="0.4">
-      <c r="A44" s="13">
+    <row r="284" spans="1:2" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A284" s="17">
         <v>45108</v>
       </c>
-      <c r="B44" s="15">
+      <c r="B284" s="19">
         <v>947</v>
       </c>
     </row>
-    <row r="45" spans="1:2" ht="16.8" x14ac:dyDescent="0.4">
-      <c r="A45" s="13">
+    <row r="285" spans="1:2" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A285" s="17">
         <v>45139</v>
       </c>
-      <c r="B45" s="15">
+      <c r="B285" s="19">
         <v>872</v>
       </c>
     </row>
-    <row r="46" spans="1:2" ht="16.8" x14ac:dyDescent="0.4">
-      <c r="A46" s="13">
+    <row r="286" spans="1:2" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A286" s="17">
         <v>45170</v>
       </c>
-      <c r="B46" s="15">
+      <c r="B286" s="19">
         <v>849</v>
       </c>
     </row>
-    <row r="47" spans="1:2" ht="16.8" x14ac:dyDescent="0.4">
-      <c r="A47" s="13">
+    <row r="287" spans="1:2" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A287" s="17">
         <v>45200</v>
       </c>
-      <c r="B47" s="15">
+      <c r="B287" s="19">
         <v>1157.4584732241142</v>
       </c>
     </row>
-    <row r="48" spans="1:2" ht="16.8" x14ac:dyDescent="0.4">
-      <c r="A48" s="13">
+    <row r="288" spans="1:2" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A288" s="17">
         <v>45231</v>
       </c>
-      <c r="B48" s="15">
+      <c r="B288" s="19">
         <v>1282.1066366773907</v>
       </c>
     </row>
-    <row r="49" spans="1:2" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A49" s="16">
+    <row r="289" spans="1:2" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A289" s="20">
         <v>45261</v>
       </c>
-      <c r="B49" s="17">
+      <c r="B289" s="21">
         <v>1220</v>
       </c>
     </row>
-    <row r="50" spans="1:2" ht="16.8" x14ac:dyDescent="0.4">
-      <c r="A50" s="11">
+    <row r="290" spans="1:2" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A290" s="15">
         <v>45292</v>
       </c>
-      <c r="B50" s="18">
+      <c r="B290" s="22">
         <v>959</v>
       </c>
     </row>
-    <row r="51" spans="1:2" ht="16.8" x14ac:dyDescent="0.4">
-      <c r="A51" s="13">
+    <row r="291" spans="1:2" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A291" s="17">
         <v>45323</v>
       </c>
-      <c r="B51" s="15">
+      <c r="B291" s="19">
         <v>961</v>
       </c>
     </row>
-    <row r="52" spans="1:2" ht="16.8" x14ac:dyDescent="0.4">
-      <c r="A52" s="13">
+    <row r="292" spans="1:2" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A292" s="17">
         <v>45352</v>
       </c>
-      <c r="B52" s="10">
+      <c r="B292" s="14">
         <v>865.53256330144438</v>
       </c>
     </row>
-    <row r="53" spans="1:2" ht="16.8" x14ac:dyDescent="0.4">
-      <c r="A53" s="13">
+    <row r="293" spans="1:2" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A293" s="17">
         <v>45383</v>
       </c>
-      <c r="B53" s="10">
+      <c r="B293" s="14">
         <v>742</v>
       </c>
     </row>
-    <row r="54" spans="1:2" ht="16.8" x14ac:dyDescent="0.4">
-      <c r="A54" s="13">
+    <row r="294" spans="1:2" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A294" s="17">
         <v>45413</v>
       </c>
-      <c r="B54" s="10">
+      <c r="B294" s="14">
         <v>1120</v>
       </c>
     </row>
-    <row r="55" spans="1:2" ht="16.8" x14ac:dyDescent="0.4">
-      <c r="A55" s="13">
+    <row r="295" spans="1:2" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A295" s="17">
         <v>45444</v>
       </c>
-      <c r="B55" s="10">
+      <c r="B295" s="14">
         <v>1172</v>
       </c>
     </row>
-    <row r="56" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A56" s="13">
+    <row r="296" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A296" s="17">
         <v>45474</v>
       </c>
-      <c r="B56" s="19">
+      <c r="B296" s="23">
         <v>1158.8837518134924</v>
       </c>
     </row>
-    <row r="57" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A57" s="13">
+    <row r="297" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A297" s="17">
         <v>45505</v>
       </c>
-      <c r="B57" s="19">
+      <c r="B297" s="23">
         <v>1049</v>
       </c>
     </row>
-    <row r="58" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A58" s="13">
+    <row r="298" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A298" s="17">
         <v>45536</v>
       </c>
-      <c r="B58" s="19">
+      <c r="B298" s="23">
         <v>1071.2334084844454</v>
       </c>
     </row>
-    <row r="59" spans="1:2" ht="16.8" x14ac:dyDescent="0.4">
-      <c r="A59" s="13">
+    <row r="299" spans="1:2" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A299" s="17">
         <v>45566</v>
       </c>
-      <c r="B59" s="10">
+      <c r="B299" s="14">
         <v>1339.1550080564646</v>
       </c>
     </row>
-    <row r="60" spans="1:2" ht="16.8" x14ac:dyDescent="0.4">
-      <c r="A60" s="13">
+    <row r="300" spans="1:2" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A300" s="17">
         <v>45597</v>
       </c>
-      <c r="B60" s="10">
+      <c r="B300" s="14">
         <v>1761.409522227121</v>
       </c>
     </row>
-    <row r="61" spans="1:2" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A61" s="13">
+    <row r="301" spans="1:2" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A301" s="17">
         <v>45627</v>
       </c>
-      <c r="B61" s="10">
+      <c r="B301" s="14">
         <v>1798.2305515042488</v>
       </c>
     </row>
-    <row r="62" spans="1:2" ht="16.8" x14ac:dyDescent="0.4">
-      <c r="A62" s="21">
+    <row r="302" spans="1:2" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A302" s="25">
         <v>45658</v>
       </c>
-      <c r="B62" s="20">
+      <c r="B302" s="24">
         <v>1355.7671534537501</v>
       </c>
     </row>
-    <row r="63" spans="1:2" ht="16.8" x14ac:dyDescent="0.4">
-      <c r="A63" s="22">
+    <row r="303" spans="1:2" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A303" s="26">
         <v>45689</v>
       </c>
-      <c r="B63" s="10">
+      <c r="B303" s="14">
         <v>1361.3928100799765</v>
       </c>
     </row>
-    <row r="64" spans="1:2" ht="16.8" x14ac:dyDescent="0.4">
-      <c r="A64" s="22">
+    <row r="304" spans="1:2" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A304" s="26">
         <v>45717</v>
       </c>
-      <c r="B64" s="10">
+      <c r="B304" s="14">
         <v>1063.9383960067662</v>
       </c>
     </row>
-    <row r="65" spans="1:2" ht="16.8" x14ac:dyDescent="0.4">
-      <c r="A65" s="22">
+    <row r="305" spans="1:2" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A305" s="26">
         <v>45748</v>
       </c>
-      <c r="B65" s="10">
+      <c r="B305" s="14">
         <v>702.81673912146914</v>
       </c>
     </row>
-    <row r="66" spans="1:2" ht="16.8" x14ac:dyDescent="0.4">
-      <c r="A66" s="22">
+    <row r="306" spans="1:2" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A306" s="26">
         <v>45778</v>
       </c>
-      <c r="B66" s="10">
+      <c r="B306" s="14">
         <v>818.64129322341682</v>
       </c>
     </row>
-    <row r="67" spans="1:2" ht="16.8" x14ac:dyDescent="0.4">
-      <c r="A67" s="22">
+    <row r="307" spans="1:2" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A307" s="26">
         <v>45809</v>
       </c>
-      <c r="B67" s="10">
+      <c r="B307" s="14">
         <v>909.10299077313323</v>
       </c>
     </row>
-    <row r="68" spans="1:2" ht="16.8" x14ac:dyDescent="0.4">
-      <c r="A68" s="22">
+    <row r="308" spans="1:2" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A308" s="26">
         <v>45839</v>
       </c>
-      <c r="B68" s="10">
+      <c r="B308" s="14">
         <v>1373.3559660678761</v>
       </c>
     </row>
-    <row r="69" spans="1:2" ht="16.8" x14ac:dyDescent="0.4">
-      <c r="A69" s="22">
+    <row r="309" spans="1:2" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A309" s="26">
         <v>45870</v>
       </c>
-      <c r="B69" s="10">
+      <c r="B309" s="14">
         <v>1242.7417498826601</v>
       </c>
     </row>
-    <row r="70" spans="1:2" ht="16.8" x14ac:dyDescent="0.4">
-      <c r="A70" s="22">
+    <row r="310" spans="1:2" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A310" s="26">
         <v>45901</v>
       </c>
-      <c r="B70" s="10">
+      <c r="B310" s="14">
         <v>1142.412575389382</v>
       </c>
     </row>
-    <row r="71" spans="1:2" ht="16.8" x14ac:dyDescent="0.4">
-      <c r="A71" s="22">
+    <row r="311" spans="1:2" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A311" s="26">
         <v>45931</v>
       </c>
-      <c r="B71" s="10">
+      <c r="B311" s="14">
         <v>1208.0865004082771</v>
       </c>
     </row>
-    <row r="72" spans="1:2" ht="16.8" x14ac:dyDescent="0.4">
-      <c r="A72" s="22">
+    <row r="312" spans="1:2" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A312" s="26">
         <v>45962</v>
       </c>
-      <c r="B72" s="10">
+      <c r="B312" s="14">
         <v>1266.0696378998325</v>
       </c>
     </row>
-    <row r="73" spans="1:2" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A73" s="23">
+    <row r="313" spans="1:2" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A313" s="27">
         <v>45992</v>
       </c>
-      <c r="B73" s="24">
+      <c r="B313" s="28">
         <v>1233.4231694949574</v>
       </c>
     </row>
-    <row r="74" spans="1:2" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A74" s="23">
+    <row r="314" spans="1:2" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A314" s="27">
         <v>46023</v>
       </c>
-      <c r="B74" s="25">
+      <c r="B314" s="29">
         <v>892.72766807250969</v>
       </c>
     </row>
